--- a/excel_bin/姓名角色表.xlsx
+++ b/excel_bin/姓名角色表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\program\PythonProject3_20260226\excel_bin\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FCB67B-44EE-406E-B25F-14BC79F8714E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -191,9 +197,6 @@
     <t>刘义航</t>
   </si>
   <si>
-    <t>设计人员、2016接口工程师</t>
-  </si>
-  <si>
     <t>崔梦飞</t>
   </si>
   <si>
@@ -303,19 +306,17 @@
   </si>
   <si>
     <t>曾添君</t>
+  </si>
+  <si>
+    <t>设计人员、2016接口工程师、2416接口工程师</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,352 +343,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -710,256 +388,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -967,76 +403,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2 3" xfId="49"/>
+    <cellStyle name="常规 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1294,14 +687,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B80"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="42.75" customWidth="1"/>
   </cols>
@@ -1678,13 +1071,13 @@
       <c r="A47" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B47" t="s">
-        <v>54</v>
+      <c r="B47" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
@@ -1692,15 +1085,15 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
         <v>56</v>
-      </c>
-      <c r="B49" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
@@ -1708,7 +1101,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
@@ -1716,7 +1109,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
@@ -1724,7 +1117,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
         <v>1</v>
@@ -1732,7 +1125,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
@@ -1740,7 +1133,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
         <v>1</v>
@@ -1748,7 +1141,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
         <v>1</v>
@@ -1756,7 +1149,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
@@ -1764,7 +1157,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
         <v>1</v>
@@ -1772,7 +1165,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" t="s">
         <v>1</v>
@@ -1780,7 +1173,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
         <v>1</v>
@@ -1788,7 +1181,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" t="s">
         <v>1</v>
@@ -1796,15 +1189,15 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B63" t="s">
         <v>1</v>
@@ -1812,7 +1205,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B64" t="s">
         <v>1</v>
@@ -1820,7 +1213,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B65" t="s">
         <v>1</v>
@@ -1828,7 +1221,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B66" t="s">
         <v>1</v>
@@ -1836,7 +1229,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
         <v>1</v>
@@ -1844,7 +1237,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B68" t="s">
         <v>1</v>
@@ -1852,15 +1245,15 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
@@ -1868,7 +1261,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B71" t="s">
         <v>1</v>
@@ -1876,7 +1269,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" t="s">
         <v>1</v>
@@ -1884,7 +1277,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B73" t="s">
         <v>1</v>
@@ -1892,7 +1285,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B74" t="s">
         <v>1</v>
@@ -1900,54 +1293,54 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" t="s">
         <v>89</v>
-      </c>
-      <c r="B79" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B80" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/excel_bin/姓名角色表.xlsx
+++ b/excel_bin/姓名角色表.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\program\PythonProject3_20260226\excel_bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FCB67B-44EE-406E-B25F-14BC79F8714E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA93737-A225-48C6-B48D-49E8CBFD377B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="94">
   <si>
     <t>张翼飞</t>
   </si>
@@ -158,9 +145,6 @@
     <t>王银平</t>
   </si>
   <si>
-    <t>设计人员、2026接口工程师</t>
-  </si>
-  <si>
     <t>许文龙</t>
   </si>
   <si>
@@ -197,15 +181,15 @@
     <t>刘义航</t>
   </si>
   <si>
+    <t>设计人员、2016接口工程师、2416接口工程师</t>
+  </si>
+  <si>
     <t>崔梦飞</t>
   </si>
   <si>
     <t>李子香</t>
   </si>
   <si>
-    <t>设计人员、1818接口工程师</t>
-  </si>
-  <si>
     <t>周凌海</t>
   </si>
   <si>
@@ -269,6 +253,9 @@
     <t>靳鹏</t>
   </si>
   <si>
+    <t>许雪松</t>
+  </si>
+  <si>
     <t>纪雨青</t>
   </si>
   <si>
@@ -308,15 +295,23 @@
     <t>曾添君</t>
   </si>
   <si>
-    <t>设计人员、2016接口工程师、2416接口工程师</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>设计人员、1818接口工程师、2026接口工程师</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>password</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>二室主任</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,14 +338,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -395,7 +397,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -416,11 +418,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -693,654 +698,905 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B80"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:C81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="42.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
+      <c r="C13" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
+      <c r="C15" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="C24" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:2">
+      <c r="C25" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="C26" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="C27" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="C28" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B29" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="C29" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="C30" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="C31" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
+      <c r="C32" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+      <c r="B33" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="C34" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:2">
+      <c r="C35" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="1" t="s">
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B37" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
+      <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="1" t="s">
+      <c r="B39" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B39" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
+      <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
+      <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="6" t="s">
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B43" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="3" t="s">
+      <c r="B44" t="s">
         <v>49</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="6" t="s">
+      <c r="B45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B45" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="6" t="s">
+      <c r="B46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B46" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="6" t="s">
+      <c r="B47" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+      <c r="C47" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="C48" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="1" t="s">
+      <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B50" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="4" t="s">
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B51" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="4" t="s">
+      <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B52" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="4" t="s">
+      <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B53" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="4" t="s">
+      <c r="B54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B54" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="4" t="s">
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B55" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="4" t="s">
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B56" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="4" t="s">
+      <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B57" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="6" t="s">
+      <c r="B58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B58" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="6" t="s">
+      <c r="B59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B59" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="6" t="s">
+      <c r="B60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="3" t="s">
+      <c r="B61" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B61" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="1" t="s">
+      <c r="B62" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="C62" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="6" t="s">
+      <c r="B63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B63" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="6" t="s">
+      <c r="B64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B64" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="6" t="s">
+      <c r="B65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B65" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="3" t="s">
+      <c r="B66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B66" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="1" t="s">
+      <c r="B67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B67" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="1" t="s">
+      <c r="B68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B68" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="6" t="s">
+      <c r="B69" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B70" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="6" t="s">
+      <c r="B71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B71" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="1" t="s">
+      <c r="B72" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B72" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="1" t="s">
+      <c r="B73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B73" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="1" t="s">
+      <c r="B74" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B74" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="1" t="s">
+      <c r="B75" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="77" spans="1:2">
+      <c r="C76" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="7" t="s">
-        <v>87</v>
+      <c r="C77" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="1" t="s">
+      <c r="C78" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="1" t="s">
+      <c r="C80" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B80" t="s">
-        <v>1</v>
+      <c r="B81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>